--- a/data/nzd0178/nzd0178.xlsx
+++ b/data/nzd0178/nzd0178.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G542"/>
+  <dimension ref="A1:G545"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14991,7 +14991,7 @@
         <v>314.78</v>
       </c>
       <c r="C541" t="n">
-        <v>361.68</v>
+        <v>366.61</v>
       </c>
       <c r="D541" t="n">
         <v>393.25</v>
@@ -15018,7 +15018,7 @@
         <v>315.08</v>
       </c>
       <c r="C542" t="n">
-        <v>359.72</v>
+        <v>364.03</v>
       </c>
       <c r="D542" t="n">
         <v>390.09</v>
@@ -15032,6 +15032,87 @@
       <c r="G542" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:33+00:00</t>
+        </is>
+      </c>
+      <c r="B543" t="n">
+        <v>324.13</v>
+      </c>
+      <c r="C543" t="n">
+        <v>375.54</v>
+      </c>
+      <c r="D543" t="n">
+        <v>391.52</v>
+      </c>
+      <c r="E543" t="n">
+        <v>392.84</v>
+      </c>
+      <c r="F543" t="n">
+        <v>388.73</v>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:06:18+00:00</t>
+        </is>
+      </c>
+      <c r="B544" t="n">
+        <v>328.75</v>
+      </c>
+      <c r="C544" t="n">
+        <v>379.3</v>
+      </c>
+      <c r="D544" t="n">
+        <v>393.33</v>
+      </c>
+      <c r="E544" t="n">
+        <v>394.65</v>
+      </c>
+      <c r="F544" t="n">
+        <v>389.12</v>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-16 22:06:24+00:00</t>
+        </is>
+      </c>
+      <c r="B545" t="n">
+        <v>334.14</v>
+      </c>
+      <c r="C545" t="n">
+        <v>377.41</v>
+      </c>
+      <c r="D545" t="n">
+        <v>389.78</v>
+      </c>
+      <c r="E545" t="n">
+        <v>394.08</v>
+      </c>
+      <c r="F545" t="n">
+        <v>387.72</v>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -15046,7 +15127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B621"/>
+  <dimension ref="A1:B624"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21259,6 +21340,36 @@
       </c>
       <c r="B621" t="n">
         <v>0.29</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B622" t="n">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B623" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>2025-12-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B624" t="n">
+        <v>0.25</v>
       </c>
     </row>
   </sheetData>
@@ -21427,28 +21538,28 @@
         <v>0.0955</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7940658471310468</v>
+        <v>0.7780856561254527</v>
       </c>
       <c r="J2" t="n">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="K2" t="n">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09497098618408983</v>
+        <v>0.09232528925564965</v>
       </c>
       <c r="M2" t="n">
-        <v>14.49692088210243</v>
+        <v>14.48531204213889</v>
       </c>
       <c r="N2" t="n">
-        <v>337.0206789401922</v>
+        <v>336.3476228472533</v>
       </c>
       <c r="O2" t="n">
-        <v>18.35812296887109</v>
+        <v>18.33978251908275</v>
       </c>
       <c r="P2" t="n">
-        <v>322.2712003494229</v>
+        <v>322.4310387535016</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -21509,28 +21620,28 @@
         <v>0.0465</v>
       </c>
       <c r="I3" t="n">
-        <v>1.829176217441731</v>
+        <v>1.837900920562553</v>
       </c>
       <c r="J3" t="n">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="K3" t="n">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1727495021702438</v>
+        <v>0.1760125866614106</v>
       </c>
       <c r="M3" t="n">
-        <v>24.16659840543098</v>
+        <v>24.0281496026352</v>
       </c>
       <c r="N3" t="n">
-        <v>910.505625880522</v>
+        <v>905.1759471826855</v>
       </c>
       <c r="O3" t="n">
-        <v>30.17458576153982</v>
+        <v>30.08614211198713</v>
       </c>
       <c r="P3" t="n">
-        <v>324.3833664493009</v>
+        <v>324.2965549050232</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -21591,28 +21702,28 @@
         <v>0.037</v>
       </c>
       <c r="I4" t="n">
-        <v>1.127807424622209</v>
+        <v>1.133532797379985</v>
       </c>
       <c r="J4" t="n">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="K4" t="n">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2475318286661324</v>
+        <v>0.2517397120384682</v>
       </c>
       <c r="M4" t="n">
-        <v>11.09851087659342</v>
+        <v>11.0601159544919</v>
       </c>
       <c r="N4" t="n">
-        <v>216.5051401047801</v>
+        <v>215.4616891859529</v>
       </c>
       <c r="O4" t="n">
-        <v>14.71411363639618</v>
+        <v>14.6786133263995</v>
       </c>
       <c r="P4" t="n">
-        <v>356.6722331114142</v>
+        <v>356.6149324969684</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21669,28 +21780,28 @@
         <v>0.043</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8264028642995283</v>
+        <v>0.8344602632622012</v>
       </c>
       <c r="J5" t="n">
+        <v>544</v>
+      </c>
+      <c r="K5" t="n">
         <v>541</v>
       </c>
-      <c r="K5" t="n">
-        <v>538</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.2604691384865706</v>
+        <v>0.2662734254452604</v>
       </c>
       <c r="M5" t="n">
-        <v>8.025435257115099</v>
+        <v>8.021081027831045</v>
       </c>
       <c r="N5" t="n">
-        <v>107.4112928930896</v>
+        <v>107.0934056089641</v>
       </c>
       <c r="O5" t="n">
-        <v>10.36394195724241</v>
+        <v>10.34859437841508</v>
       </c>
       <c r="P5" t="n">
-        <v>364.9378197983101</v>
+        <v>364.8564947108475</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -21747,28 +21858,28 @@
         <v>0.0438</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7840662568128319</v>
+        <v>0.7894709816072834</v>
       </c>
       <c r="J6" t="n">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="K6" t="n">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1570459800564949</v>
+        <v>0.1605310106722323</v>
       </c>
       <c r="M6" t="n">
-        <v>10.70956286415281</v>
+        <v>10.6770961818795</v>
       </c>
       <c r="N6" t="n">
-        <v>184.7667494415095</v>
+        <v>183.8734285942915</v>
       </c>
       <c r="O6" t="n">
-        <v>13.59289334326984</v>
+        <v>13.55999367972904</v>
       </c>
       <c r="P6" t="n">
-        <v>363.0149615891301</v>
+        <v>362.9608671253775</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21806,7 +21917,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G542"/>
+  <dimension ref="A1:G545"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41722,7 +41833,7 @@
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>-36.83575325935519,174.42708947958377</t>
+          <t>-36.8357689633129,174.42703776868134</t>
         </is>
       </c>
       <c r="D541" t="inlineStr">
@@ -41759,7 +41870,7 @@
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>-36.835747015990606,174.42711003807037</t>
+          <t>-36.835760745017296,174.42706483037335</t>
         </is>
       </c>
       <c r="D542" t="inlineStr">
@@ -41780,6 +41891,117 @@
       <c r="G542" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:33+00:00</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>-36.836308543917134,174.42779303028286</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>-36.835797408762225,174.426944101616</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>-36.83517340717383,174.42646680376834</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>-36.83450270205609,174.42614327551553</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>-36.83381469472259,174.4258767016884</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:06:18+00:00</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>-36.836323260650154,174.4277445707555</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>-36.83580938577183,174.42690466283022</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>-36.835179172643656,174.4264478187325</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>-36.83450846748966,174.4261242906262</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>-36.833815936992686,174.42587261105535</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-16 22:06:24+00:00</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>-36.8363404301475,174.427688034616</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>-36.83580336541488,174.4269244871151</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>-36.835167864675206,174.4264850545735</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>-36.834506651856216,174.4261302692933</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>-36.83381147756088,174.42588729537846</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>

--- a/data/nzd0178/nzd0178.xlsx
+++ b/data/nzd0178/nzd0178.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G545"/>
+  <dimension ref="A1:G549"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15105,7 +15105,7 @@
         <v>389.78</v>
       </c>
       <c r="E545" t="n">
-        <v>394.08</v>
+        <v>391.8</v>
       </c>
       <c r="F545" t="n">
         <v>387.72</v>
@@ -15113,6 +15113,114 @@
       <c r="G545" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:06:17+00:00</t>
+        </is>
+      </c>
+      <c r="B546" t="n">
+        <v>337.86</v>
+      </c>
+      <c r="C546" t="n">
+        <v>379.74</v>
+      </c>
+      <c r="D546" t="n">
+        <v>391.21</v>
+      </c>
+      <c r="E546" t="n">
+        <v>392.76</v>
+      </c>
+      <c r="F546" t="n">
+        <v>388.62</v>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:06:25+00:00</t>
+        </is>
+      </c>
+      <c r="B547" t="n">
+        <v>341.07</v>
+      </c>
+      <c r="C547" t="n">
+        <v>382.35</v>
+      </c>
+      <c r="D547" t="n">
+        <v>392.85</v>
+      </c>
+      <c r="E547" t="n">
+        <v>393.48</v>
+      </c>
+      <c r="F547" t="n">
+        <v>389.37</v>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B548" t="n">
+        <v>344.9</v>
+      </c>
+      <c r="C548" t="n">
+        <v>385.49</v>
+      </c>
+      <c r="D548" t="n">
+        <v>394.32</v>
+      </c>
+      <c r="E548" t="n">
+        <v>395.51</v>
+      </c>
+      <c r="F548" t="n">
+        <v>391.32</v>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-16 22:12:21+00:00</t>
+        </is>
+      </c>
+      <c r="B549" t="n">
+        <v>347.48</v>
+      </c>
+      <c r="C549" t="n">
+        <v>387.19</v>
+      </c>
+      <c r="D549" t="n">
+        <v>395.1</v>
+      </c>
+      <c r="E549" t="n">
+        <v>395.33</v>
+      </c>
+      <c r="F549" t="n">
+        <v>391.01</v>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -15127,7 +15235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B624"/>
+  <dimension ref="A1:B628"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21370,6 +21478,46 @@
       </c>
       <c r="B624" t="n">
         <v>0.25</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B625" t="n">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B626" t="n">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B627" t="n">
+        <v>-0.58</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>2026-01-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B628" t="n">
+        <v>0.74</v>
       </c>
     </row>
   </sheetData>
@@ -21538,28 +21686,28 @@
         <v>0.0955</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7780856561254527</v>
+        <v>0.7778040132801679</v>
       </c>
       <c r="J2" t="n">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="K2" t="n">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09232528925564965</v>
+        <v>0.09368286367603929</v>
       </c>
       <c r="M2" t="n">
-        <v>14.48531204213889</v>
+        <v>14.40354130423083</v>
       </c>
       <c r="N2" t="n">
-        <v>336.3476228472533</v>
+        <v>333.9812845980787</v>
       </c>
       <c r="O2" t="n">
-        <v>18.33978251908275</v>
+        <v>18.27515484470867</v>
       </c>
       <c r="P2" t="n">
-        <v>322.4310387535016</v>
+        <v>322.4338095925028</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -21620,28 +21768,28 @@
         <v>0.0465</v>
       </c>
       <c r="I3" t="n">
-        <v>1.837900920562553</v>
+        <v>1.853718637077528</v>
       </c>
       <c r="J3" t="n">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="K3" t="n">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1760125866614106</v>
+        <v>0.1808676647150725</v>
       </c>
       <c r="M3" t="n">
-        <v>24.0281496026352</v>
+        <v>23.90681547281043</v>
       </c>
       <c r="N3" t="n">
-        <v>905.1759471826855</v>
+        <v>899.3109993219692</v>
       </c>
       <c r="O3" t="n">
-        <v>30.08614211198713</v>
+        <v>29.98851445673775</v>
       </c>
       <c r="P3" t="n">
-        <v>324.2965549050232</v>
+        <v>324.1380416924005</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -21702,28 +21850,28 @@
         <v>0.037</v>
       </c>
       <c r="I4" t="n">
-        <v>1.133532797379985</v>
+        <v>1.143463141792654</v>
       </c>
       <c r="J4" t="n">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="K4" t="n">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2517397120384682</v>
+        <v>0.2580016403047856</v>
       </c>
       <c r="M4" t="n">
-        <v>11.0601159544919</v>
+        <v>11.01927776731236</v>
       </c>
       <c r="N4" t="n">
-        <v>215.4616891859529</v>
+        <v>214.226716877693</v>
       </c>
       <c r="O4" t="n">
-        <v>14.6786133263995</v>
+        <v>14.63648581038813</v>
       </c>
       <c r="P4" t="n">
-        <v>356.6149324969684</v>
+        <v>356.5152206681962</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21780,28 +21928,28 @@
         <v>0.043</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8344602632622012</v>
+        <v>0.8444984254148218</v>
       </c>
       <c r="J5" t="n">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="K5" t="n">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2662734254452604</v>
+        <v>0.2737391560250139</v>
       </c>
       <c r="M5" t="n">
-        <v>8.021081027831045</v>
+        <v>8.01228553040408</v>
       </c>
       <c r="N5" t="n">
-        <v>107.0934056089641</v>
+        <v>106.652420927348</v>
       </c>
       <c r="O5" t="n">
-        <v>10.34859437841508</v>
+        <v>10.32726589796874</v>
       </c>
       <c r="P5" t="n">
-        <v>364.8564947108475</v>
+        <v>364.7548454070794</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -21858,28 +22006,28 @@
         <v>0.0438</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7894709816072834</v>
+        <v>0.798625650653744</v>
       </c>
       <c r="J6" t="n">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="K6" t="n">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1605310106722323</v>
+        <v>0.1658036393513057</v>
       </c>
       <c r="M6" t="n">
-        <v>10.6770961818795</v>
+        <v>10.64400279150109</v>
       </c>
       <c r="N6" t="n">
-        <v>183.8734285942915</v>
+        <v>182.8140438538642</v>
       </c>
       <c r="O6" t="n">
-        <v>13.55999367972904</v>
+        <v>13.52087437460552</v>
       </c>
       <c r="P6" t="n">
-        <v>362.9608671253775</v>
+        <v>362.8689488149747</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21917,7 +22065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G545"/>
+  <dimension ref="A1:G549"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41991,7 +42139,7 @@
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>-36.834506651856216,174.4261302692933</t>
+          <t>-36.83449938931944,174.42615418395891</t>
         </is>
       </c>
       <c r="F545" t="inlineStr">
@@ -42002,6 +42150,154 @@
       <c r="G545" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:06:17+00:00</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>-36.83635227995217,174.42764901522443</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>-36.83581078733595,174.42690004765237</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>-36.83517241971739,174.42647005534877</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>-36.834502447230236,174.4261441146266</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>-36.83381434433868,174.42587785545666</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:06:25+00:00</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>-36.83636250517674,174.4276153452556</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>-36.835819101155835,174.42687267125268</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>-36.83517764367957,174.42645285343843</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>-36.83450474066279,174.42613656262682</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>-36.83381673331961,174.42586998885463</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>-36.83637470535454,174.4275751720408</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>-36.83582910321447,174.4268397356527</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>-36.8351823261314,174.4264374346509</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>-36.8345112068659,174.42611527018053</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>-36.83382294466763,174.42584953568692</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-16 22:12:21+00:00</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>-36.836382923743585,174.4275481101811</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>-36.83583451833801,174.4268219042732</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>-36.83518481069689,174.42642925325262</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>-36.83451063350814,174.42611715818086</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>-36.83382195722279,174.42585278721637</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>

--- a/data/nzd0178/nzd0178.xlsx
+++ b/data/nzd0178/nzd0178.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G549"/>
+  <dimension ref="A1:G550"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15219,6 +15219,33 @@
         <v>391.01</v>
       </c>
       <c r="G549" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:02+00:00</t>
+        </is>
+      </c>
+      <c r="B550" t="n">
+        <v>356.82</v>
+      </c>
+      <c r="C550" t="n">
+        <v>388.7</v>
+      </c>
+      <c r="D550" t="n">
+        <v>395.07</v>
+      </c>
+      <c r="E550" t="n">
+        <v>396.39</v>
+      </c>
+      <c r="F550" t="n">
+        <v>390.76</v>
+      </c>
+      <c r="G550" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -15235,7 +15262,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B628"/>
+  <dimension ref="A1:B629"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21518,6 +21545,16 @@
       </c>
       <c r="B628" t="n">
         <v>0.74</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B629" t="n">
+        <v>-0.47</v>
       </c>
     </row>
   </sheetData>
@@ -21686,28 +21723,28 @@
         <v>0.0955</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7778040132801679</v>
+        <v>0.7828594653479102</v>
       </c>
       <c r="J2" t="n">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="K2" t="n">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09368286367603929</v>
+        <v>0.0950673128244568</v>
       </c>
       <c r="M2" t="n">
-        <v>14.40354130423083</v>
+        <v>14.40506169127928</v>
       </c>
       <c r="N2" t="n">
-        <v>333.9812845980787</v>
+        <v>333.7126450317054</v>
       </c>
       <c r="O2" t="n">
-        <v>18.27515484470867</v>
+        <v>18.26780350867902</v>
       </c>
       <c r="P2" t="n">
-        <v>322.4338095925028</v>
+        <v>322.3828705105329</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -21768,28 +21805,28 @@
         <v>0.0465</v>
       </c>
       <c r="I3" t="n">
-        <v>1.853718637077528</v>
+        <v>1.859361571228584</v>
       </c>
       <c r="J3" t="n">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="K3" t="n">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1808676647150725</v>
+        <v>0.1823286256611999</v>
       </c>
       <c r="M3" t="n">
-        <v>23.90681547281043</v>
+        <v>23.88277858621821</v>
       </c>
       <c r="N3" t="n">
-        <v>899.3109993219692</v>
+        <v>898.0677597228798</v>
       </c>
       <c r="O3" t="n">
-        <v>29.98851445673775</v>
+        <v>29.96777869183633</v>
       </c>
       <c r="P3" t="n">
-        <v>324.1380416924005</v>
+        <v>324.0812597056236</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -21850,28 +21887,28 @@
         <v>0.037</v>
       </c>
       <c r="I4" t="n">
-        <v>1.143463141792654</v>
+        <v>1.146476260399991</v>
       </c>
       <c r="J4" t="n">
+        <v>549</v>
+      </c>
+      <c r="K4" t="n">
         <v>548</v>
       </c>
-      <c r="K4" t="n">
-        <v>547</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.2580016403047856</v>
+        <v>0.2597217162830767</v>
       </c>
       <c r="M4" t="n">
-        <v>11.01927776731236</v>
+        <v>11.01133114916056</v>
       </c>
       <c r="N4" t="n">
-        <v>214.226716877693</v>
+        <v>213.9569875198482</v>
       </c>
       <c r="O4" t="n">
-        <v>14.63648581038813</v>
+        <v>14.62726862814272</v>
       </c>
       <c r="P4" t="n">
-        <v>356.5152206681962</v>
+        <v>356.4848435218564</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21928,28 +21965,28 @@
         <v>0.043</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8444984254148218</v>
+        <v>0.8479201719450414</v>
       </c>
       <c r="J5" t="n">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="K5" t="n">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2737391560250139</v>
+        <v>0.2759179722321836</v>
       </c>
       <c r="M5" t="n">
-        <v>8.01228553040408</v>
+        <v>8.014559207528436</v>
       </c>
       <c r="N5" t="n">
-        <v>106.652420927348</v>
+        <v>106.6109775973512</v>
       </c>
       <c r="O5" t="n">
-        <v>10.32726589796874</v>
+        <v>10.32525920242931</v>
       </c>
       <c r="P5" t="n">
-        <v>364.7548454070794</v>
+        <v>364.7200622186863</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22006,28 +22043,28 @@
         <v>0.0438</v>
       </c>
       <c r="I6" t="n">
-        <v>0.798625650653744</v>
+        <v>0.8010840553351859</v>
       </c>
       <c r="J6" t="n">
+        <v>549</v>
+      </c>
+      <c r="K6" t="n">
         <v>548</v>
       </c>
-      <c r="K6" t="n">
-        <v>547</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.1658036393513057</v>
+        <v>0.1671877918756547</v>
       </c>
       <c r="M6" t="n">
-        <v>10.64400279150109</v>
+        <v>10.63658152983139</v>
       </c>
       <c r="N6" t="n">
-        <v>182.8140438538642</v>
+        <v>182.5611205085926</v>
       </c>
       <c r="O6" t="n">
-        <v>13.52087437460552</v>
+        <v>13.51151806824802</v>
       </c>
       <c r="P6" t="n">
-        <v>362.8689488149747</v>
+        <v>362.8441640890802</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -22065,7 +22102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G549"/>
+  <dimension ref="A1:G550"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42301,6 +42338,43 @@
         </is>
       </c>
     </row>
+    <row r="550">
+      <c r="A550" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:02+00:00</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>-36.83641267553543,174.42745014200352</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>-36.83583932823967,174.4268060658104</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>-36.835184715136684,174.4264295679218</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>-36.83451400994786,174.42610603995635</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>-36.83382116089624,174.42585540941747</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0178/nzd0178.xlsx
+++ b/data/nzd0178/nzd0178.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G550"/>
+  <dimension ref="A1:G552"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15246,6 +15246,60 @@
         <v>390.76</v>
       </c>
       <c r="G550" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:11:50+00:00</t>
+        </is>
+      </c>
+      <c r="B551" t="n">
+        <v>358.74</v>
+      </c>
+      <c r="C551" t="n">
+        <v>390.47</v>
+      </c>
+      <c r="D551" t="n">
+        <v>395.94</v>
+      </c>
+      <c r="E551" t="n">
+        <v>395.68</v>
+      </c>
+      <c r="F551" t="n">
+        <v>390.6</v>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:06:01+00:00</t>
+        </is>
+      </c>
+      <c r="B552" t="n">
+        <v>364.27</v>
+      </c>
+      <c r="C552" t="n">
+        <v>391.73</v>
+      </c>
+      <c r="D552" t="n">
+        <v>396.23</v>
+      </c>
+      <c r="E552" t="n">
+        <v>395.39</v>
+      </c>
+      <c r="F552" t="n">
+        <v>390.03</v>
+      </c>
+      <c r="G552" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -15262,7 +15316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B629"/>
+  <dimension ref="A1:B631"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21555,6 +21609,26 @@
       </c>
       <c r="B629" t="n">
         <v>-0.47</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B630" t="n">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B631" t="n">
+        <v>-0.38</v>
       </c>
     </row>
   </sheetData>
@@ -21723,28 +21797,28 @@
         <v>0.0955</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7828594653479102</v>
+        <v>0.7962234381702497</v>
       </c>
       <c r="J2" t="n">
+        <v>551</v>
+      </c>
+      <c r="K2" t="n">
         <v>549</v>
       </c>
-      <c r="K2" t="n">
-        <v>547</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.0950673128244568</v>
+        <v>0.09844308739062979</v>
       </c>
       <c r="M2" t="n">
-        <v>14.40506169127928</v>
+        <v>14.42656052481184</v>
       </c>
       <c r="N2" t="n">
-        <v>333.7126450317054</v>
+        <v>333.7298446112038</v>
       </c>
       <c r="O2" t="n">
-        <v>18.26780350867902</v>
+        <v>18.26827426472473</v>
       </c>
       <c r="P2" t="n">
-        <v>322.3828705105329</v>
+        <v>322.2480229534384</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -21805,28 +21879,28 @@
         <v>0.0465</v>
       </c>
       <c r="I3" t="n">
-        <v>1.859361571228584</v>
+        <v>1.872187032005997</v>
       </c>
       <c r="J3" t="n">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="K3" t="n">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1823286256611999</v>
+        <v>0.1854648908092084</v>
       </c>
       <c r="M3" t="n">
-        <v>23.88277858621821</v>
+        <v>23.84046572585999</v>
       </c>
       <c r="N3" t="n">
-        <v>898.0677597228798</v>
+        <v>895.8631603665524</v>
       </c>
       <c r="O3" t="n">
-        <v>29.96777869183633</v>
+        <v>29.93097326126487</v>
       </c>
       <c r="P3" t="n">
-        <v>324.0812597056236</v>
+        <v>323.9520230470555</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -21887,28 +21961,28 @@
         <v>0.037</v>
       </c>
       <c r="I4" t="n">
-        <v>1.146476260399991</v>
+        <v>1.153126816279529</v>
       </c>
       <c r="J4" t="n">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="K4" t="n">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2597217162830767</v>
+        <v>0.2633244985662466</v>
       </c>
       <c r="M4" t="n">
-        <v>11.01133114916056</v>
+        <v>10.99795732273761</v>
       </c>
       <c r="N4" t="n">
-        <v>213.9569875198482</v>
+        <v>213.4769360115823</v>
       </c>
       <c r="O4" t="n">
-        <v>14.62726862814272</v>
+        <v>14.61084994145044</v>
       </c>
       <c r="P4" t="n">
-        <v>356.4848435218564</v>
+        <v>356.4177049614864</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21965,28 +22039,28 @@
         <v>0.043</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8479201719450414</v>
+        <v>0.85400981727198</v>
       </c>
       <c r="J5" t="n">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="K5" t="n">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2759179722321836</v>
+        <v>0.2800370776356383</v>
       </c>
       <c r="M5" t="n">
-        <v>8.014559207528436</v>
+        <v>8.015475860869163</v>
       </c>
       <c r="N5" t="n">
-        <v>106.6109775973512</v>
+        <v>106.4679346918186</v>
       </c>
       <c r="O5" t="n">
-        <v>10.32525920242931</v>
+        <v>10.31833003406165</v>
       </c>
       <c r="P5" t="n">
-        <v>364.7200622186863</v>
+        <v>364.6580775897523</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22043,28 +22117,28 @@
         <v>0.0438</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8010840553351859</v>
+        <v>0.8055859339734479</v>
       </c>
       <c r="J6" t="n">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="K6" t="n">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1671877918756547</v>
+        <v>0.1698415156148589</v>
       </c>
       <c r="M6" t="n">
-        <v>10.63658152983139</v>
+        <v>10.6197440384909</v>
       </c>
       <c r="N6" t="n">
-        <v>182.5611205085926</v>
+        <v>182.0341033027259</v>
       </c>
       <c r="O6" t="n">
-        <v>13.51151806824802</v>
+        <v>13.49200145651956</v>
       </c>
       <c r="P6" t="n">
-        <v>362.8441640890802</v>
+        <v>362.798718294207</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -22102,7 +22176,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G550"/>
+  <dimension ref="A1:G552"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42375,6 +42449,80 @@
         </is>
       </c>
     </row>
+    <row r="551">
+      <c r="A551" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:11:50+00:00</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>-36.83641879152564,174.4274300029252</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>-36.83584496633367,174.42678750019252</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>-36.83518748638217,174.42642044251545</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>-36.83451174837044,174.4261134870691</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>-36.83382065124722,174.42585708762616</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:06:01+00:00</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>-36.83643640683292,174.42737199816554</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>-36.835848979890365,174.4267742839882</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>-36.835188410130506,174.42641740071315</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>-36.83451082462739,174.42611652884742</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>-36.8338188356224,174.42586306624437</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0178/nzd0178.xlsx
+++ b/data/nzd0178/nzd0178.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G552"/>
+  <dimension ref="A1:G554"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15300,6 +15300,60 @@
         <v>390.03</v>
       </c>
       <c r="G552" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:35+00:00</t>
+        </is>
+      </c>
+      <c r="B553" t="n">
+        <v>380.96</v>
+      </c>
+      <c r="C553" t="n">
+        <v>405.5</v>
+      </c>
+      <c r="D553" t="n">
+        <v>402.49</v>
+      </c>
+      <c r="E553" t="n">
+        <v>397.25</v>
+      </c>
+      <c r="F553" t="n">
+        <v>391.77</v>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B554" t="n">
+        <v>376.49</v>
+      </c>
+      <c r="C554" t="n">
+        <v>405.5</v>
+      </c>
+      <c r="D554" t="n">
+        <v>401.05</v>
+      </c>
+      <c r="E554" t="n">
+        <v>395.88</v>
+      </c>
+      <c r="F554" t="n">
+        <v>389.36</v>
+      </c>
+      <c r="G554" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -15316,7 +15370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B631"/>
+  <dimension ref="A1:B634"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21629,6 +21683,36 @@
       </c>
       <c r="B631" t="n">
         <v>-0.38</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B632" t="n">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B633" t="n">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B634" t="n">
+        <v>0.91</v>
       </c>
     </row>
   </sheetData>
@@ -21797,28 +21881,28 @@
         <v>0.0955</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7962234381702497</v>
+        <v>0.8219154342793724</v>
       </c>
       <c r="J2" t="n">
+        <v>553</v>
+      </c>
+      <c r="K2" t="n">
         <v>551</v>
       </c>
-      <c r="K2" t="n">
-        <v>549</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.09844308739062979</v>
+        <v>0.103782052649296</v>
       </c>
       <c r="M2" t="n">
-        <v>14.42656052481184</v>
+        <v>14.5165140555202</v>
       </c>
       <c r="N2" t="n">
-        <v>333.7298446112038</v>
+        <v>336.9754344809632</v>
       </c>
       <c r="O2" t="n">
-        <v>18.26827426472473</v>
+        <v>18.35689065394691</v>
       </c>
       <c r="P2" t="n">
-        <v>322.2480229534384</v>
+        <v>321.9872378500423</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -21879,28 +21963,28 @@
         <v>0.0465</v>
       </c>
       <c r="I3" t="n">
-        <v>1.872187032005997</v>
+        <v>1.895182264255481</v>
       </c>
       <c r="J3" t="n">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="K3" t="n">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1854648908092084</v>
+        <v>0.1898631410393686</v>
       </c>
       <c r="M3" t="n">
-        <v>23.84046572585999</v>
+        <v>23.83422290373318</v>
       </c>
       <c r="N3" t="n">
-        <v>895.8631603665524</v>
+        <v>896.1712086199714</v>
       </c>
       <c r="O3" t="n">
-        <v>29.93097326126487</v>
+        <v>29.93611879686429</v>
       </c>
       <c r="P3" t="n">
-        <v>323.9520230470555</v>
+        <v>323.7188747237799</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -21961,28 +22045,28 @@
         <v>0.037</v>
       </c>
       <c r="I4" t="n">
-        <v>1.153126816279529</v>
+        <v>1.163728471269825</v>
       </c>
       <c r="J4" t="n">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="K4" t="n">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2633244985662466</v>
+        <v>0.2678718972810241</v>
       </c>
       <c r="M4" t="n">
-        <v>10.99795732273761</v>
+        <v>11.00071275202364</v>
       </c>
       <c r="N4" t="n">
-        <v>213.4769360115823</v>
+        <v>213.4595132357927</v>
       </c>
       <c r="O4" t="n">
-        <v>14.61084994145044</v>
+        <v>14.61025370196537</v>
       </c>
       <c r="P4" t="n">
-        <v>356.4177049614864</v>
+        <v>356.310036333679</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22039,28 +22123,28 @@
         <v>0.043</v>
       </c>
       <c r="I5" t="n">
-        <v>0.85400981727198</v>
+        <v>0.8606961096594941</v>
       </c>
       <c r="J5" t="n">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="K5" t="n">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2800370776356383</v>
+        <v>0.2843721022065102</v>
       </c>
       <c r="M5" t="n">
-        <v>8.015475860869163</v>
+        <v>8.018996176597236</v>
       </c>
       <c r="N5" t="n">
-        <v>106.4679346918186</v>
+        <v>106.3778708209014</v>
       </c>
       <c r="O5" t="n">
-        <v>10.31833003406165</v>
+        <v>10.31396484485483</v>
       </c>
       <c r="P5" t="n">
-        <v>364.6580775897523</v>
+        <v>364.5896137709204</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22117,28 +22201,28 @@
         <v>0.0438</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8055859339734479</v>
+        <v>0.8101299207254049</v>
       </c>
       <c r="J6" t="n">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="K6" t="n">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1698415156148589</v>
+        <v>0.1725394181049081</v>
       </c>
       <c r="M6" t="n">
-        <v>10.6197440384909</v>
+        <v>10.60312020251255</v>
       </c>
       <c r="N6" t="n">
-        <v>182.0341033027259</v>
+        <v>181.5183777100429</v>
       </c>
       <c r="O6" t="n">
-        <v>13.49200145651956</v>
+        <v>13.47287562883451</v>
       </c>
       <c r="P6" t="n">
-        <v>362.798718294207</v>
+        <v>362.7525707102318</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -22176,7 +22260,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G552"/>
+  <dimension ref="A1:G554"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42523,6 +42607,80 @@
         </is>
       </c>
     </row>
+    <row r="553">
+      <c r="A553" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:35+00:00</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>-36.836489571127025,174.4271969348096</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>-36.8358928422375,174.42662984966276</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>-36.83520835033472,174.42635173972153</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>-36.83451674932274,174.42609701950934</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>-36.83382437805514,174.42584481572467</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>-36.836475332422395,174.42724382118524</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>-36.8358928422375,174.42662984966276</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>-36.83520376345383,174.4263668438505</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>-36.834512385434536,174.42611138929092</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>-36.833816701466546,174.42587009374265</t>
+        </is>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0178/nzd0178.xlsx
+++ b/data/nzd0178/nzd0178.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G554"/>
+  <dimension ref="A1:G560"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15308,54 +15308,216 @@
     <row r="553">
       <c r="A553" s="1" t="inlineStr">
         <is>
-          <t>2026-04-14 22:11:35+00:00</t>
+          <t>2026-04-15 22:05:35+00:00</t>
         </is>
       </c>
       <c r="B553" t="n">
-        <v>380.96</v>
+        <v>386.89</v>
       </c>
       <c r="C553" t="n">
         <v>405.5</v>
       </c>
       <c r="D553" t="n">
-        <v>402.49</v>
+        <v>405.98</v>
       </c>
       <c r="E553" t="n">
-        <v>397.25</v>
+        <v>400.03</v>
       </c>
       <c r="F553" t="n">
-        <v>391.77</v>
+        <v>394.68</v>
       </c>
       <c r="G553" t="inlineStr">
         <is>
-          <t>L9</t>
+          <t>L8</t>
         </is>
       </c>
     </row>
     <row r="554">
       <c r="A554" s="1" t="inlineStr">
         <is>
-          <t>2026-04-15 22:05:35+00:00</t>
+          <t>2026-04-22 22:11:44+00:00</t>
         </is>
       </c>
       <c r="B554" t="n">
-        <v>376.49</v>
+        <v>390.25</v>
       </c>
       <c r="C554" t="n">
-        <v>405.5</v>
+        <v>408.19</v>
       </c>
       <c r="D554" t="n">
-        <v>401.05</v>
+        <v>409.12</v>
       </c>
       <c r="E554" t="n">
-        <v>395.88</v>
+        <v>400.03</v>
       </c>
       <c r="F554" t="n">
-        <v>389.36</v>
+        <v>396.32</v>
       </c>
       <c r="G554" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:54+00:00</t>
+        </is>
+      </c>
+      <c r="B555" t="n">
+        <v>390.25</v>
+      </c>
+      <c r="C555" t="n">
+        <v>408.19</v>
+      </c>
+      <c r="D555" t="n">
+        <v>409.42</v>
+      </c>
+      <c r="E555" t="n">
+        <v>399.49</v>
+      </c>
+      <c r="F555" t="n">
+        <v>395.22</v>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:29+00:00</t>
+        </is>
+      </c>
+      <c r="B556" t="n">
+        <v>390.25</v>
+      </c>
+      <c r="C556" t="n">
+        <v>408.19</v>
+      </c>
+      <c r="D556" t="n">
+        <v>409.32</v>
+      </c>
+      <c r="E556" t="n">
+        <v>399.39</v>
+      </c>
+      <c r="F556" t="n">
+        <v>394.65</v>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B557" t="n">
+        <v>391.73</v>
+      </c>
+      <c r="C557" t="n">
+        <v>408.5</v>
+      </c>
+      <c r="D557" t="n">
+        <v>408.92</v>
+      </c>
+      <c r="E557" t="n">
+        <v>398.1</v>
+      </c>
+      <c r="F557" t="n">
+        <v>393.44</v>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B558" t="n">
+        <v>386.89</v>
+      </c>
+      <c r="C558" t="n">
+        <v>408.5</v>
+      </c>
+      <c r="D558" t="n">
+        <v>409.53</v>
+      </c>
+      <c r="E558" t="n">
+        <v>398.44</v>
+      </c>
+      <c r="F558" t="n">
+        <v>393.28</v>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B559" t="n">
+        <v>383.1</v>
+      </c>
+      <c r="C559" t="n">
+        <v>408.5</v>
+      </c>
+      <c r="D559" t="n">
+        <v>410.39</v>
+      </c>
+      <c r="E559" t="n">
+        <v>398.83</v>
+      </c>
+      <c r="F559" t="n">
+        <v>393.72</v>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:05:20+00:00</t>
+        </is>
+      </c>
+      <c r="B560" t="n">
+        <v>377.53</v>
+      </c>
+      <c r="C560" t="n">
+        <v>409.15</v>
+      </c>
+      <c r="D560" t="n">
+        <v>410.88</v>
+      </c>
+      <c r="E560" t="n">
+        <v>400.38</v>
+      </c>
+      <c r="F560" t="n">
+        <v>395.13</v>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -15370,7 +15532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B634"/>
+  <dimension ref="A1:B641"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21713,6 +21875,76 @@
       </c>
       <c r="B634" t="n">
         <v>0.91</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B635" t="n">
+        <v>-0.39</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B636" t="n">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B637" t="n">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B638" t="n">
+        <v>-0.61</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B639" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B640" t="n">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B641" t="n">
+        <v>-0.58</v>
       </c>
     </row>
   </sheetData>
@@ -21881,28 +22113,28 @@
         <v>0.0955</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8219154342793724</v>
+        <v>0.9194423588088533</v>
       </c>
       <c r="J2" t="n">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="K2" t="n">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="L2" t="n">
-        <v>0.103782052649296</v>
+        <v>0.1224102221371302</v>
       </c>
       <c r="M2" t="n">
-        <v>14.5165140555202</v>
+        <v>14.90384674975582</v>
       </c>
       <c r="N2" t="n">
-        <v>336.9754344809632</v>
+        <v>355.1530010252351</v>
       </c>
       <c r="O2" t="n">
-        <v>18.35689065394691</v>
+        <v>18.84550346966711</v>
       </c>
       <c r="P2" t="n">
-        <v>321.9872378500423</v>
+        <v>320.9944194629273</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -21963,28 +22195,28 @@
         <v>0.0465</v>
       </c>
       <c r="I3" t="n">
-        <v>1.895182264255481</v>
+        <v>1.968385095672122</v>
       </c>
       <c r="J3" t="n">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="K3" t="n">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1898631410393686</v>
+        <v>0.2035702665668565</v>
       </c>
       <c r="M3" t="n">
-        <v>23.83422290373318</v>
+        <v>23.83291617859673</v>
       </c>
       <c r="N3" t="n">
-        <v>896.1712086199714</v>
+        <v>898.8538008476205</v>
       </c>
       <c r="O3" t="n">
-        <v>29.93611879686429</v>
+        <v>29.98089059463745</v>
       </c>
       <c r="P3" t="n">
-        <v>323.7188747237799</v>
+        <v>322.9742349563414</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -22045,28 +22277,28 @@
         <v>0.037</v>
       </c>
       <c r="I4" t="n">
-        <v>1.163728471269825</v>
+        <v>1.215084513188007</v>
       </c>
       <c r="J4" t="n">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="K4" t="n">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2678718972810241</v>
+        <v>0.2847489685932449</v>
       </c>
       <c r="M4" t="n">
-        <v>11.00071275202364</v>
+        <v>11.09541840442238</v>
       </c>
       <c r="N4" t="n">
-        <v>213.4595132357927</v>
+        <v>216.978436027151</v>
       </c>
       <c r="O4" t="n">
-        <v>14.61025370196537</v>
+        <v>14.73018791554103</v>
       </c>
       <c r="P4" t="n">
-        <v>356.310036333679</v>
+        <v>355.7869213570159</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22123,28 +22355,28 @@
         <v>0.043</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8606961096594941</v>
+        <v>0.8877076920876978</v>
       </c>
       <c r="J5" t="n">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="K5" t="n">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2843721022065102</v>
+        <v>0.2992202731864994</v>
       </c>
       <c r="M5" t="n">
-        <v>8.018996176597236</v>
+        <v>8.064146839229128</v>
       </c>
       <c r="N5" t="n">
-        <v>106.3778708209014</v>
+        <v>106.8495107254015</v>
       </c>
       <c r="O5" t="n">
-        <v>10.31396484485483</v>
+        <v>10.33680369966469</v>
       </c>
       <c r="P5" t="n">
-        <v>364.5896137709204</v>
+        <v>364.3122241306687</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22201,28 +22433,28 @@
         <v>0.0438</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8101299207254049</v>
+        <v>0.8343765614284482</v>
       </c>
       <c r="J6" t="n">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="K6" t="n">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1725394181049081</v>
+        <v>0.1838217621743334</v>
       </c>
       <c r="M6" t="n">
-        <v>10.60312020251255</v>
+        <v>10.60653291854496</v>
       </c>
       <c r="N6" t="n">
-        <v>181.5183777100429</v>
+        <v>180.8504307228573</v>
       </c>
       <c r="O6" t="n">
-        <v>13.47287562883451</v>
+        <v>13.44806419983401</v>
       </c>
       <c r="P6" t="n">
-        <v>362.7525707102318</v>
+        <v>362.5056470812094</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -22260,7 +22492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G554"/>
+  <dimension ref="A1:G560"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42610,12 +42842,12 @@
     <row r="553">
       <c r="A553" s="1" t="inlineStr">
         <is>
-          <t>2026-04-14 22:11:35+00:00</t>
+          <t>2026-04-15 22:05:35+00:00</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>-36.836489571127025,174.4271969348096</t>
+          <t>-36.836508460476765,174.42713473428807</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
@@ -42625,59 +42857,281 @@
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>-36.83520835033472,174.42635173972153</t>
+          <t>-36.83521946714238,174.426315133179</t>
         </is>
       </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>-36.83451674932274,174.42609701950934</t>
+          <t>-36.83452560450668,174.42606786038536</t>
         </is>
       </c>
       <c r="F553" t="inlineStr">
         <is>
-          <t>-36.83382437805514,174.42584481572467</t>
+          <t>-36.83383364728996,174.42581429329766</t>
         </is>
       </c>
       <c r="G553" t="inlineStr">
         <is>
-          <t>L9</t>
+          <t>L8</t>
         </is>
       </c>
     </row>
     <row r="554">
       <c r="A554" s="1" t="inlineStr">
         <is>
-          <t>2026-04-15 22:05:35+00:00</t>
+          <t>2026-04-22 22:11:44+00:00</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>-36.836475332422395,174.42724382118524</t>
+          <t>-36.83651916336562,174.42709949080825</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>-36.8358928422375,174.42662984966276</t>
+          <t>-36.83590141082406,174.42660163407754</t>
         </is>
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>-36.83520376345383,174.4263668438505</t>
+          <t>-36.83522946907446,174.42628219777038</t>
         </is>
       </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>-36.834512385434536,174.42611138929092</t>
+          <t>-36.83452560450668,174.42606786038536</t>
         </is>
       </c>
       <c r="F554" t="inlineStr">
         <is>
-          <t>-36.833816701466546,174.42587009374265</t>
+          <t>-36.83383887118524,174.42579709165165</t>
         </is>
       </c>
       <c r="G554" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:54+00:00</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>-36.83651916336562,174.42709949080825</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>-36.83590141082406,174.42660163407754</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>-36.8352304246726,174.42627905107483</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>-36.83452388443553,174.4260735243884</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>-36.833835367353316,174.42580862934133</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:29+00:00</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>-36.83651916336562,174.42709949080825</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>-36.83590141082406,174.42660163407754</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>-36.8352301061399,174.42628009997335</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>-36.834523565903794,174.42607457327784</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>-36.83383355173088,174.4258146079619</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>-36.836523877730095,174.4270839668913</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>-36.835902398281554,174.42659838246692</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>-36.835228832008994,174.42628429556737</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>-36.83451945684375,174.4260881039506</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>-36.83382969751387,174.4258272994187</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>-36.836508460476765,174.42713473428807</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>-36.835902398281554,174.42659838246692</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>-36.83523077505857,174.42627789728644</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>-36.83452053985197,174.42608453772692</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>-36.833829187865234,174.42582897762776</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>-36.83649638786063,174.42717448808202</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>-36.835902398281554,174.42659838246692</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>-36.83523351443936,174.42626887675863</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>-36.834521782125975,174.42608044705844</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>-36.833830589398914,174.42582436255276</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:05:20+00:00</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>-36.836478645232255,174.4272329124999</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>-36.835904468756695,174.4265915645734</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>-36.835235075249045,174.42626373715532</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>-36.83452671936745,174.42606418927215</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>-36.833835080676096,174.42580957333408</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
